--- a/files/九龙-红磡-首岸第2期.xlsx
+++ b/files/九龙-红磡-首岸第2期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,7 +121,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -195,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -257,7 +263,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -634,11 +643,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -5159,7 +5168,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5571,7 +5580,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5633,7 +5642,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5695,34 +5704,34 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>8398000</v>
+        <v>7642100</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>24773</v>
+        <v>22543</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>7642180</v>
+        <v>7642100</v>
       </c>
       <c r="L74" s="5" t="n">
         <v>22543</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -7367,7 +7376,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -7779,7 +7788,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7841,7 +7850,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7903,7 +7912,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -8245,7 +8254,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8447,34 +8456,34 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>16862000</v>
+        <v>15344400</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>25548</v>
+        <v>23249</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>15344420</v>
+        <v>15344400</v>
       </c>
       <c r="L114" s="5" t="n">
         <v>23249</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -9349,7 +9358,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9971,7 +9980,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -10033,7 +10042,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -10095,7 +10104,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -10647,34 +10656,34 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>16679000</v>
+        <v>15177800</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>25271</v>
+        <v>22997</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>15177890</v>
+        <v>15177800</v>
       </c>
       <c r="L146" s="5" t="n">
         <v>22997</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
@@ -12179,7 +12188,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -12241,7 +12250,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -12303,7 +12312,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -12645,7 +12654,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -12847,7 +12856,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12979,7 +12988,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -13251,7 +13260,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -13313,7 +13322,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -13375,7 +13384,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13927,7 +13936,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -14829,7 +14838,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -15171,7 +15180,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -15443,7 +15452,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15505,7 +15514,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -15567,7 +15576,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -15979,34 +15988,34 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
-        <v>10463000</v>
+        <v>9521300</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>24220</v>
+        <v>22040</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K224" s="5" t="n">
-        <v>9521330</v>
+        <v>9521300</v>
       </c>
       <c r="L224" s="5" t="n">
         <v>22040</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -16111,7 +16120,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -16523,7 +16532,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -16585,7 +16594,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -16647,7 +16656,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -17269,7 +17278,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -17331,7 +17340,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -18093,7 +18102,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -18155,34 +18164,34 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
-        <v>10333000</v>
+        <v>9403000</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>23919</v>
+        <v>21766</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K256" s="5" t="n">
-        <v>9403030</v>
+        <v>9403000</v>
       </c>
       <c r="L256" s="5" t="n">
         <v>21766</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
@@ -18287,34 +18296,34 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
-        <v>15925000</v>
+        <v>14491700</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>24129</v>
+        <v>21957</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>14491750</v>
+        <v>14491700</v>
       </c>
       <c r="L258" s="5" t="n">
         <v>21957</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -18349,7 +18358,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18411,7 +18420,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -18683,7 +18692,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -18745,7 +18754,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -19157,34 +19166,34 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
-        <v>8661000</v>
+        <v>7881500</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>21927</v>
+        <v>19953</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K271" s="5" t="n">
-        <v>7881510</v>
+        <v>7881500</v>
       </c>
       <c r="L271" s="5" t="n">
         <v>19953</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
@@ -19219,7 +19228,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -19351,23 +19360,23 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
-        <v>15830000</v>
+        <v>14405300</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>23985</v>
+        <v>21826</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K274" s="5" t="n">
@@ -19378,7 +19387,7 @@
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
@@ -19763,7 +19772,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -19825,34 +19834,34 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>7675000</v>
+        <v>6984200</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>22640</v>
+        <v>20602</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>6984250</v>
+        <v>6984200</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>20603</v>
+        <v>20602</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -20517,7 +20526,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -20579,7 +20588,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -21411,7 +21420,7 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -21613,7 +21622,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -21955,7 +21964,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -22017,34 +22026,34 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
-        <v>7503000</v>
+        <v>6827700</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>22133</v>
+        <v>20141</v>
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K313" s="5" t="n">
-        <v>6827730</v>
+        <v>6827700</v>
       </c>
       <c r="L313" s="5" t="n">
         <v>20141</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N313" s="3" t="inlineStr">
@@ -22499,7 +22508,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -22631,7 +22640,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -22693,23 +22702,23 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
-        <v>8700000</v>
+        <v>7917000</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>22835</v>
+        <v>20780</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
@@ -22720,7 +22729,7 @@
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N323" s="3" t="inlineStr">
@@ -22755,7 +22764,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -23027,7 +23036,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -23089,23 +23098,23 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
-        <v>7430000</v>
+        <v>6761300</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>21917</v>
+        <v>19945</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K329" s="5" t="n">
@@ -23116,7 +23125,7 @@
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -23571,7 +23580,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -23703,7 +23712,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -24605,34 +24614,34 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
-        <v>8306000</v>
+        <v>7724500</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>21028</v>
+        <v>19556</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K351" s="5" t="n">
-        <v>7558460</v>
+        <v>7724500</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>19135</v>
+        <v>19556</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N351" s="3" t="inlineStr">
@@ -24667,7 +24676,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -24799,7 +24808,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -24931,7 +24940,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -25203,7 +25212,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -25265,34 +25274,34 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
-        <v>7324000</v>
+        <v>6664800</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>21605</v>
+        <v>19660</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K361" s="5" t="n">
-        <v>6664840</v>
+        <v>6664800</v>
       </c>
       <c r="L361" s="5" t="n">
         <v>19660</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N361" s="3" t="inlineStr">
@@ -25327,34 +25336,34 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
-        <v>7346000</v>
+        <v>6684800</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>21670</v>
+        <v>19719</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K362" s="5" t="n">
-        <v>6684860</v>
+        <v>6684800</v>
       </c>
       <c r="L362" s="5" t="n">
         <v>19719</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N362" s="3" t="inlineStr">
@@ -25669,34 +25678,34 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
-        <v>8236000</v>
+        <v>7494700</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>20851</v>
+        <v>18974</v>
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K367" s="5" t="n">
-        <v>7494760</v>
+        <v>7494700</v>
       </c>
       <c r="L367" s="5" t="n">
         <v>18974</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N367" s="3" t="inlineStr">
@@ -25731,7 +25740,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -25863,7 +25872,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -25925,34 +25934,34 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
-        <v>8960000</v>
+        <v>8332800</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>26122</v>
+        <v>24294</v>
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>8153600</v>
+        <v>8332800</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>23771</v>
+        <v>24294</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N371" s="3" t="inlineStr">
@@ -25987,23 +25996,23 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
-        <v>8720000</v>
+        <v>7935200</v>
       </c>
       <c r="I372" s="5" t="n">
-        <v>24773</v>
+        <v>22543</v>
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
@@ -26014,7 +26023,7 @@
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -26259,7 +26268,7 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -26321,7 +26330,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -26383,7 +26392,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -26725,7 +26734,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -26787,7 +26796,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -27047,17 +27056,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27574,7 +27583,7 @@
           <t>A | 660呎 (3房)
 $1713万
 $25,959/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -27768,12 +27777,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
-$840万
-$24,773/呎
-(已定价未售)</t>
+$764万
+$22,543/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -27781,7 +27790,7 @@
           <t>K | 339呎 (2房)
 $839万
 $24,749/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -27789,7 +27798,7 @@
           <t>L | 339呎 (2房)
 $838万
 $24,723/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -27844,7 +27853,7 @@
           <t>A | 660呎 (3房)
 $1695万
 $25,677/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -27974,12 +27983,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 660呎 (3房)
-$1686万
-$25,548/呎
-(已定价未售)</t>
+$1534万
+$23,249/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28003,7 +28012,7 @@
           <t>D | 395呎 (2房)
 $964万
 $24,403/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -28043,7 +28052,7 @@
           <t>J | 339呎 (2房)
 $834万
 $24,605/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -28051,7 +28060,7 @@
           <t>K | 339呎 (2房)
 $833万
 $24,578/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -28059,7 +28068,7 @@
           <t>L | 339呎 (2房)
 $832万
 $24,549/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -28138,7 +28147,7 @@
           <t>D | 395呎 (2房)
 $956万
 $24,213/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -28244,12 +28253,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 660呎 (3房)
-$1668万
-$25,271/呎
-(已定价未售)</t>
+$1518万
+$22,997/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -28313,7 +28322,7 @@
           <t>J | 339呎 (2房)
 $825万
 $24,333/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -28321,7 +28330,7 @@
           <t>K | 339呎 (2房)
 $824万
 $24,307/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -28329,7 +28338,7 @@
           <t>L | 339呎 (2房)
 $823万
 $24,280/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -28519,7 +28528,7 @@
           <t>A | 660呎 (3房)
 $1652万
 $25,036/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -28543,7 +28552,7 @@
           <t>D | 395呎 (2房)
 $931万
 $23,580/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -28583,7 +28592,7 @@
           <t>J | 339呎 (2房)
 $812万
 $23,956/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -28591,7 +28600,7 @@
           <t>K | 339呎 (2房)
 $811万
 $23,932/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -28599,7 +28608,7 @@
           <t>L | 339呎 (2房)
 $810万
 $23,906/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -28654,7 +28663,7 @@
           <t>A | 660呎 (3房)
 $1642万
 $24,879/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -28718,7 +28727,7 @@
           <t>J | 339呎 (2房)
 $806万
 $23,782/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -28726,7 +28735,7 @@
           <t>K | 339呎 (2房)
 $805万
 $23,755/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -28734,7 +28743,7 @@
           <t>L | 339呎 (2房)
 $804万
 $23,729/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -28766,7 +28775,7 @@
           <t>Q | 389呎 (2房)
 $900万
 $23,134/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q16" s="20" t="inlineStr">
@@ -28813,7 +28822,7 @@
           <t>D | 395呎 (2房)
 $911万
 $23,056/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -28924,7 +28933,7 @@
           <t>A | 660呎 (3房)
 $1618万
 $24,515/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -28935,12 +28944,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 432呎 (2房)
-$1046万
-$24,220/呎
-(已定价未售)</t>
+$952万
+$22,040/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -28988,7 +28997,7 @@
           <t>J | 339呎 (2房)
 $793万
 $23,398/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -28996,7 +29005,7 @@
           <t>K | 339呎 (2房)
 $792万
 $23,378/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -29004,7 +29013,7 @@
           <t>L | 339呎 (2房)
 $792万
 $23,351/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -29036,7 +29045,7 @@
           <t>Q | 389呎 (2房)
 $890万
 $22,884/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q18" s="20" t="inlineStr">
@@ -29123,7 +29132,7 @@
           <t>J | 339呎 (2房)
 $788万
 $23,254/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -29131,7 +29140,7 @@
           <t>K | 339呎 (2房)
 $787万
 $23,227/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -29139,7 +29148,7 @@
           <t>L | 339呎 (2房)
 $786万
 $23,201/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -29189,12 +29198,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 660呎 (3房)
-$1592万
-$24,129/呎
-(已定价未售)</t>
+$1449万
+$21,957/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -29205,12 +29214,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 432呎 (2房)
-$1033万
-$23,919/呎
-(已定价未售)</t>
+$940万
+$21,766/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -29218,7 +29227,7 @@
           <t>D | 395呎 (2房)
 $873万
 $22,109/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -29306,7 +29315,7 @@
           <t>Q | 389呎 (2房)
 $879万
 $22,602/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q20" s="21" t="inlineStr">
@@ -29314,7 +29323,7 @@
           <t>R | 381呎 (2房)
 $893万
 $23,438/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29324,12 +29333,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 660呎 (3房)
-$1583万
-$23,985/呎
-(已定价未售)</t>
+$1441万
+$21,826/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -29345,15 +29354,15 @@
           <t>C | 432呎 (2房)
 $1027万
 $23,773/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 395呎 (2房)
-$866万
-$21,927/呎
-(已定价未售)</t>
+$788万
+$19,953/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -29401,7 +29410,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,885/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -29409,7 +29418,7 @@
           <t>L | 339呎 (2房)
 $775万
 $22,858/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -29441,7 +29450,7 @@
           <t>Q | 389呎 (2房)
 $873万
 $22,442/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q21" s="21" t="inlineStr">
@@ -29449,7 +29458,7 @@
           <t>R | 381呎 (2房)
 $889万
 $23,336/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29531,12 +29540,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
-$768万
-$22,640/呎
-(已定价未售)</t>
+$698万
+$20,602/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -29544,7 +29553,7 @@
           <t>L | 339呎 (2房)
 $767万
 $22,614/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -29615,7 +29624,7 @@
           <t>C | 432呎 (2房)
 $1014万
 $23,477/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -29711,7 +29720,7 @@
           <t>Q | 389呎 (2房)
 $862万
 $22,165/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q23" s="21" t="inlineStr">
@@ -29719,7 +29728,7 @@
           <t>R | 381呎 (2房)
 $881万
 $23,126/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29743,7 @@
           <t>A | 660呎 (3房)
 $1564万
 $23,689/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -29750,7 +29759,7 @@
           <t>C | 432呎 (2房)
 $1008万
 $23,324/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -29801,12 +29810,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
-$750万
-$22,133/呎
-(已定价未售)</t>
+$683万
+$20,141/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -29814,7 +29823,7 @@
           <t>L | 339呎 (2房)
 $749万
 $22,106/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -29854,7 +29863,7 @@
           <t>R | 381呎 (2房)
 $875万
 $22,974/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -29869,7 +29878,7 @@
           <t>A | 660呎 (3房)
 $1556万
 $23,579/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -29885,7 +29894,7 @@
           <t>C | 432呎 (2房)
 $1002万
 $23,183/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -29936,12 +29945,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
-$743万
-$21,917/呎
-(已定价未售)</t>
+$676万
+$19,945/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -29949,7 +29958,7 @@
           <t>L | 339呎 (2房)
 $742万
 $21,894/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -29981,15 +29990,15 @@
           <t>Q | 389呎 (2房)
 $847万
 $21,771/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="Q25" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="Q25" s="22" t="inlineStr">
         <is>
           <t>R | 381呎 (2房)
-$870万
-$22,835/呎
-(已定价未售)</t>
+$792万
+$20,780/呎
+(26年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -30004,7 +30013,7 @@
           <t>A | 660呎 (3房)
 $1549万
 $23,476/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -30020,15 +30029,15 @@
           <t>C | 432呎 (2房)
 $995万
 $23,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 395呎 (2房)
-$831万
-$21,028/呎
-(已定价未售)</t>
+$772万
+$19,556/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -30139,7 +30148,7 @@
           <t>A | 660呎 (3房)
 $1541万
 $23,355/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -30155,15 +30164,15 @@
           <t>C | 432呎 (2房)
 $971万
 $22,472/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 395呎 (2房)
-$824万
-$20,851/呎
-(已定价未售)</t>
+$749万
+$18,974/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -30198,20 +30207,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>J | 339呎 (2房)
-$735万
-$21,670/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="inlineStr">
+$668万
+$19,719/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>K | 339呎 (2房)
-$732万
-$21,605/呎
-(已定价未售)</t>
+$666万
+$19,660/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -30219,7 +30228,7 @@
           <t>L | 339呎 (2房)
 $732万
 $21,578/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -30251,7 +30260,7 @@
           <t>Q | 389呎 (2房)
 $835万
 $21,460/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q27" s="20" t="inlineStr">
@@ -30290,7 +30299,7 @@
           <t>C | 395呎 (2房)
 $1055万
 $26,701/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -30298,7 +30307,7 @@
           <t>D | 358呎 (2房)
 $872万
 $24,372/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -30338,7 +30347,7 @@
           <t>J | 339呎 (2房)
 $726万
 $21,410/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -30346,7 +30355,7 @@
           <t>K | 339呎 (2房)
 $725万
 $21,386/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -30354,7 +30363,7 @@
           <t>L | 339呎 (2房)
 $724万
 $21,360/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr">
@@ -30381,20 +30390,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="P28" s="21" t="inlineStr">
+      <c r="P28" s="22" t="inlineStr">
         <is>
           <t>Q | 352呎 (2房)
-$872万
-$24,773/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="Q28" s="21" t="inlineStr">
+$794万
+$22,543/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>R | 343呎 (2房)
-$896万
-$26,122/呎
-(已定价未售)</t>
+$833万
+$24,294/呎
+(26年-10月-12日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首岸第2期.xlsx
+++ b/files/九龙-红磡-首岸第2期.xlsx
@@ -20526,34 +20526,34 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
-        <v>8811000</v>
+        <v>8194200</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>23126</v>
+        <v>21507</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K291" s="5" t="n">
-        <v>8018010</v>
+        <v>8194200</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>21045</v>
+        <v>21507</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N291" s="3" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29723,12 +29723,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="Q23" s="21" t="inlineStr">
+      <c r="Q23" s="22" t="inlineStr">
         <is>
           <t>R | 381呎 (2房)
-$881万
-$23,126/呎
-(在售)</t>
+$819万
+$21,507/呎
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首岸第2期.xlsx
+++ b/files/九龙-红磡-首岸第2期.xlsx
@@ -17278,23 +17278,23 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
-        <v>8930000</v>
+        <v>8126300</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>23438</v>
+        <v>21329</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
@@ -21622,34 +21622,34 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>8753000</v>
+        <v>8140200</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>22974</v>
+        <v>21365</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>7965230</v>
+        <v>8140200</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>20906</v>
+        <v>21365</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N307" s="3" t="inlineStr">
@@ -25212,34 +25212,34 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
-        <v>7315000</v>
+        <v>6656600</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>21578</v>
+        <v>19636</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>6656650</v>
+        <v>6656600</v>
       </c>
       <c r="L360" s="5" t="n">
         <v>19636</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -25740,34 +25740,34 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
-        <v>9708000</v>
+        <v>8834200</v>
       </c>
       <c r="I368" s="5" t="n">
-        <v>22472</v>
+        <v>20450</v>
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>8834280</v>
+        <v>8834200</v>
       </c>
       <c r="L368" s="5" t="n">
         <v>20450</v>
       </c>
       <c r="M368" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N368" s="3" t="inlineStr">
@@ -26268,34 +26268,34 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
-        <v>7241000</v>
+        <v>6589300</v>
       </c>
       <c r="I376" s="5" t="n">
-        <v>21360</v>
+        <v>19437</v>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K376" s="5" t="n">
-        <v>6589310</v>
+        <v>6589300</v>
       </c>
       <c r="L376" s="5" t="n">
         <v>19437</v>
       </c>
       <c r="M376" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N376" s="3" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29318,12 +29318,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="Q20" s="21" t="inlineStr">
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t>R | 381呎 (2房)
-$893万
-$23,438/呎
-(在售)</t>
+$813万
+$21,329/呎
+(26年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -29858,12 +29858,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="Q24" s="21" t="inlineStr">
+      <c r="Q24" s="22" t="inlineStr">
         <is>
           <t>R | 381呎 (2房)
-$875万
-$22,974/呎
-(在售)</t>
+$814万
+$21,365/呎
+(26年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -30159,12 +30159,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 432呎 (2房)
-$971万
-$22,472/呎
-(在售)</t>
+$883万
+$20,450/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -30223,12 +30223,12 @@
 (26年-10月-12日)</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
+      <c r="L27" s="22" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
-$732万
-$21,578/呎
-(在售)</t>
+$666万
+$19,636/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -30358,12 +30358,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="L28" s="22" t="inlineStr">
         <is>
           <t>L | 339呎 (2房)
-$724万
-$21,360/呎
-(在售)</t>
+$659万
+$19,437/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr">

--- a/files/九龙-红磡-首岸第2期.xlsx
+++ b/files/九龙-红磡-首岸第2期.xlsx
@@ -8254,34 +8254,34 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>9639000</v>
+        <v>8771400</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>24403</v>
+        <v>22206</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>8771490</v>
+        <v>8771400</v>
       </c>
       <c r="L111" s="5" t="n">
         <v>22206</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -18358,34 +18358,34 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
-        <v>8891000</v>
+        <v>8090800</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>23336</v>
+        <v>21236</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>8090810</v>
+        <v>8090800</v>
       </c>
       <c r="L259" s="5" t="n">
         <v>21236</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28007,12 +28007,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 395呎 (2房)
-$964万
-$24,403/呎
-(在售)</t>
+$877万
+$22,206/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -28949,7 +28949,7 @@
           <t>C | 432呎 (2房)
 $952万
 $22,040/呎
-(26年-10月-12日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -29453,12 +29453,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="Q21" s="21" t="inlineStr">
+      <c r="Q21" s="22" t="inlineStr">
         <is>
           <t>R | 381呎 (2房)
-$889万
-$23,336/呎
-(在售)</t>
+$809万
+$21,236/呎
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
